--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486327_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486327_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. IDEHEN IDEHEN</t>
+          <t>A. DOMENECH FONTANA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2909</v>
+        <v>1.871</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5272</v>
+        <v>1.5591</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7637</v>
+        <v>0.3119</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.6137</v>
+        <v>1.3422</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.177</v>
+        <v>0.1182</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4367</v>
+        <v>1.224</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.2079</v>
+        <v>1.8867</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5776</v>
+        <v>0.9855</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6303</v>
+        <v>0.9013</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4057</v>
+        <v>-0.5445</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5994</v>
+        <v>-0.8672</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1936</v>
+        <v>0.3227</v>
       </c>
       <c r="P2" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R2" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4696</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3447</v>
+        <v>-0.1526</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1248</v>
+        <v>0.2463</v>
       </c>
       <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.13</v>
       </c>
-      <c r="W2" t="n">
-        <v>0.3904</v>
-      </c>
       <c r="X2" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DOMENECH FONTANA</t>
+          <t>E. IDEHEN IDEHEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.522</v>
+        <v>1.3912</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0868</v>
+        <v>-0.3416</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4352</v>
+        <v>1.7328</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3422</v>
+        <v>-1.6137</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1182</v>
+        <v>-1.177</v>
       </c>
       <c r="I3" t="n">
-        <v>1.224</v>
+        <v>-0.4367</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8867</v>
+        <v>-1.2079</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9855</v>
+        <v>-0.5776</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9013</v>
+        <v>-0.6303</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5445</v>
+        <v>-0.4057</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8672</v>
+        <v>-0.5994</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3227</v>
+        <v>0.1936</v>
       </c>
       <c r="P3" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2552</v>
+        <v>0.5699</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6249</v>
+        <v>0.4759</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3696</v>
+        <v>0.094</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>0.3904</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.13</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7323</v>
+        <v>0.0185</v>
       </c>
       <c r="E4" t="n">
-        <v>2.977</v>
+        <v>2.2631</v>
       </c>
       <c r="F4" t="n">
         <v>-2.2447</v>
@@ -766,10 +766,10 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9746</v>
+        <v>0.2608</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5997</v>
+        <v>-0.1142</v>
       </c>
       <c r="U4" t="n">
         <v>0.3749</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1894</v>
+        <v>-0.2874</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.2385</v>
+        <v>-2.2132</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0491</v>
+        <v>1.9258</v>
       </c>
       <c r="G5" t="n">
         <v>-1.4476</v>
@@ -844,13 +844,13 @@
         <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3288</v>
+        <v>0.2307</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4194</v>
+        <v>-0.3941</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7482</v>
+        <v>0.6249</v>
       </c>
       <c r="V5" t="n">
         <v>1.582</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9291</v>
+        <v>-1.7921</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9668</v>
+        <v>-0.8298</v>
       </c>
       <c r="F6" t="n">
         <v>-0.9623</v>
@@ -922,10 +922,10 @@
         <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0445</v>
+        <v>0.0925</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0769</v>
+        <v>0.0601</v>
       </c>
       <c r="U6" t="n">
         <v>0.0324</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5722</v>
+        <v>-1.9141</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5931</v>
+        <v>-0.9659</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.979</v>
+        <v>-0.9482</v>
       </c>
       <c r="G7" t="n">
         <v>-2.1045</v>
@@ -1000,13 +1000,13 @@
         <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8375</v>
+        <v>-0.1794</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.548</v>
+        <v>0.0793</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2895</v>
+        <v>-0.2587</v>
       </c>
       <c r="V7" t="n">
         <v>0.3698</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8929</v>
+        <v>-2.8621</v>
       </c>
       <c r="E8" t="n">
         <v>0.0781</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.971</v>
+        <v>-2.9402</v>
       </c>
       <c r="G8" t="n">
         <v>0.8108</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0479</v>
+        <v>-0.0171</v>
       </c>
       <c r="T8" t="n">
         <v>-0.137</v>
       </c>
       <c r="U8" t="n">
-        <v>0.089</v>
+        <v>0.1199</v>
       </c>
       <c r="V8" t="n">
         <v>-2.5682</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.5889</v>
+        <v>-4.055</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3477</v>
+        <v>-2.8754</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2412</v>
+        <v>-1.1796</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7328</v>
@@ -1156,13 +1156,13 @@
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6355</v>
+        <v>-0.1015</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1644</v>
+        <v>-0.6922</v>
       </c>
       <c r="U9" t="n">
-        <v>0.529</v>
+        <v>0.5906</v>
       </c>
       <c r="V9" t="n">
         <v>-2.5682</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.5283</v>
+        <v>-5.6227</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4378</v>
+        <v>-2.6555</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0905</v>
+        <v>-2.9672</v>
       </c>
       <c r="G10" t="n">
         <v>-4.0266</v>
@@ -1234,13 +1234,13 @@
         <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9813</v>
+        <v>-0.0757</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.0288</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2278</v>
+        <v>-0.1046</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5204</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.5974</v>
+        <v>-7.4729</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.6943</v>
+        <v>-7.6006</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0969</v>
+        <v>0.1277</v>
       </c>
       <c r="G11" t="n">
         <v>0.7342</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>0.089</v>
+        <v>0.2136</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4194</v>
+        <v>-0.3256</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5084</v>
+        <v>0.5392</v>
       </c>
       <c r="V11" t="n">
         <v>-1.243</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-21.753</v>
+        <v>-20.7256</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.6091</v>
+        <v>-13.5817</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.143800000000001</v>
+        <v>-7.144</v>
       </c>
       <c r="G12" t="n">
         <v>-10.7899</v>
@@ -1390,13 +1390,13 @@
         <v>14.1378</v>
       </c>
       <c r="S12" t="n">
-        <v>0.06009999999999996</v>
+        <v>1.0875</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.1991</v>
+        <v>-1.1716</v>
       </c>
       <c r="U12" t="n">
-        <v>2.259</v>
+        <v>2.2589</v>
       </c>
       <c r="V12" t="n">
         <v>-3.4106</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.0092</v>
+        <v>7.1673</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0983</v>
+        <v>4.6571</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9109</v>
+        <v>2.5102</v>
       </c>
       <c r="G13" t="n">
         <v>2.6262</v>
@@ -1468,13 +1468,13 @@
         <v>2.6101</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1883</v>
+        <v>0.3464</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0959</v>
+        <v>-0.5371</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2842</v>
+        <v>0.8835</v>
       </c>
       <c r="V13" t="n">
         <v>3.7597</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1695</v>
+        <v>6.3429</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8791</v>
+        <v>2.9909</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2904</v>
+        <v>3.352</v>
       </c>
       <c r="G14" t="n">
         <v>-1.0701</v>
@@ -1546,13 +1546,13 @@
         <v>2.3926</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3271</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1334</v>
+        <v>-0.0216</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4605</v>
+        <v>0.5221</v>
       </c>
       <c r="V14" t="n">
         <v>4.5199</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9296</v>
+        <v>2.0855</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3108</v>
+        <v>2.7241</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2405</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5817</v>
+        <v>1.1513</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5259</v>
+        <v>-0.4472</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0558</v>
+        <v>1.5985</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3085</v>
+        <v>1.9036</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1555</v>
+        <v>0.2007</v>
       </c>
       <c r="L15" t="n">
-        <v>0.153</v>
+        <v>1.7029</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8902</v>
+        <v>-0.7523</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6814</v>
+        <v>-0.6479</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2088</v>
+        <v>-0.1044</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.0451</v>
+        <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2933</v>
+        <v>-0.3061</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2077</v>
+        <v>-0.5047</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0856</v>
+        <v>0.1986</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7395</v>
+        <v>-0.9347</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7395</v>
+        <v>1.3252</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>K. LUNDQVIST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8813</v>
+        <v>1.6642</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6124</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7311</v>
+        <v>1.5675</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1513</v>
+        <v>2.5762</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4472</v>
+        <v>3.452</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5985</v>
+        <v>-0.8757</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9036</v>
+        <v>2.817</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2007</v>
+        <v>3.5039</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7029</v>
+        <v>-0.6869</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7523</v>
+        <v>-0.2408</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6479</v>
+        <v>-0.0519</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1044</v>
+        <v>-0.1889</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1751</v>
+        <v>-0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5104</v>
+        <v>-0.2818</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6165</v>
+        <v>-0.1754</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1061</v>
+        <v>-0.1064</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9347</v>
+        <v>-0.1952</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3252</v>
+        <v>-0.3698</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.2599</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. LUNDQVIST</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6256</v>
+        <v>1.6271</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1268</v>
+        <v>-1.4284</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7524</v>
+        <v>3.0555</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5762</v>
+        <v>-0.5817</v>
       </c>
       <c r="H17" t="n">
-        <v>3.452</v>
+        <v>-0.5259</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8757</v>
+        <v>-0.0558</v>
       </c>
       <c r="J17" t="n">
-        <v>2.817</v>
+        <v>0.3085</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5039</v>
+        <v>0.1555</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6869</v>
+        <v>0.153</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2408</v>
+        <v>-0.8902</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0519</v>
+        <v>-0.6814</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1889</v>
+        <v>-0.2088</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.435</v>
+        <v>1.9576</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7401</v>
+        <v>3.0451</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3204</v>
+        <v>0.9908</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.399</v>
+        <v>0.0901</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0786</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1952</v>
+        <v>-0.7395</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3698</v>
+        <v>-0.7395</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.537</v>
+        <v>1.5255</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5236</v>
+        <v>0.6353</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0135</v>
+        <v>0.8902</v>
       </c>
       <c r="G18" t="n">
         <v>0.07829999999999999</v>
@@ -1858,13 +1858,13 @@
         <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5412</v>
+        <v>-0.5528</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6165</v>
+        <v>-0.5047</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0752</v>
+        <v>-0.0481</v>
       </c>
       <c r="V18" t="n">
         <v>1.13</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6929</v>
+        <v>1.2321</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0516</v>
+        <v>0.2886</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6414</v>
+        <v>0.9435</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1418</v>
+        <v>-0.238</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4867</v>
+        <v>-1.6636</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6551</v>
+        <v>1.4256</v>
       </c>
       <c r="J19" t="n">
-        <v>1.949</v>
+        <v>0.3343</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5721000000000001</v>
+        <v>-0.8331</v>
       </c>
       <c r="L19" t="n">
-        <v>1.377</v>
+        <v>1.1674</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1927</v>
+        <v>-0.5723</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0854</v>
+        <v>-0.8304</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2781</v>
+        <v>0.2582</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3836</v>
+        <v>0.295</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2776</v>
+        <v>-0.0457</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6612</v>
+        <v>0.3407</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6086</v>
+        <v>0.9746</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0438</v>
+        <v>0.379</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5648</v>
+        <v>0.5956</v>
       </c>
       <c r="G20" t="n">
         <v>3.1531</v>
@@ -2014,13 +2014,13 @@
         <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.805</v>
+        <v>-0.4389</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.536</v>
+        <v>-0.2007</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2691</v>
+        <v>-0.2382</v>
       </c>
       <c r="V20" t="n">
         <v>-1.3045</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5819</v>
+        <v>0.6042</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.032</v>
+        <v>-0.2837</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6139</v>
+        <v>0.8879</v>
       </c>
       <c r="G21" t="n">
-        <v>0.301</v>
+        <v>2.1418</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.146</v>
+        <v>0.4867</v>
       </c>
       <c r="I21" t="n">
-        <v>0.447</v>
+        <v>1.6551</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0365</v>
+        <v>1.949</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0365</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.377</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2645</v>
+        <v>0.1927</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1825</v>
+        <v>-0.0854</v>
       </c>
       <c r="O21" t="n">
-        <v>0.447</v>
+        <v>0.2781</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0633</v>
+        <v>-0.4723</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0577</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1318</v>
+        <v>-0.4146</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4884</v>
+        <v>0.4894</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2702</v>
+        <v>-0.032</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7585</v>
+        <v>0.5214</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.238</v>
+        <v>0.301</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6636</v>
+        <v>-0.146</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4256</v>
+        <v>0.447</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3343</v>
+        <v>0.0365</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8331</v>
+        <v>0.0365</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1674</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5723</v>
+        <v>0.2645</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8304</v>
+        <v>-0.1825</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2582</v>
+        <v>0.447</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4487</v>
+        <v>-0.0291</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6044</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1557</v>
+        <v>0.0394</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0669</v>
+        <v>-0.3598</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4737</v>
+        <v>1.0267</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5406</v>
+        <v>-1.3865</v>
       </c>
       <c r="G23" t="n">
         <v>2.9483</v>
@@ -2248,13 +2248,13 @@
         <v>0.435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1027</v>
+        <v>-0.3957</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4711</v>
+        <v>0.024</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5738</v>
+        <v>-0.4197</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2599</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.704</v>
+        <v>-1.6</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7986</v>
+        <v>-3.9104</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0946</v>
+        <v>2.3104</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2967</v>
@@ -2326,13 +2326,13 @@
         <v>2.3926</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1799</v>
+        <v>0.2839</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1454</v>
+        <v>-0.2572</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3253</v>
+        <v>0.5411</v>
       </c>
       <c r="V24" t="n">
         <v>0.1952</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>21.7531</v>
+        <v>21.753</v>
       </c>
       <c r="E25" t="n">
-        <v>7.144100000000002</v>
+        <v>7.143899999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>14.6092</v>
+        <v>14.6091</v>
       </c>
       <c r="G25" t="n">
         <v>10.7897</v>
@@ -2380,7 +2380,7 @@
         <v>13.6996</v>
       </c>
       <c r="K25" t="n">
-        <v>6.495800000000001</v>
+        <v>6.4958</v>
       </c>
       <c r="L25" t="n">
         <v>7.203900000000001</v>
@@ -2401,16 +2401,16 @@
         <v>-14.138</v>
       </c>
       <c r="R25" t="n">
-        <v>21.75089999999999</v>
+        <v>21.7509</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.06010000000000043</v>
+        <v>-0.06009999999999999</v>
       </c>
       <c r="T25" t="n">
         <v>-2.2592</v>
       </c>
       <c r="U25" t="n">
-        <v>2.1989</v>
+        <v>2.1991</v>
       </c>
       <c r="V25" t="n">
         <v>3.4108</v>
